--- a/Caracterizacion_Haces/data/z0mm-822.xlsx
+++ b/Caracterizacion_Haces/data/z0mm-822.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opticacuantica\Documents\Mateo Rubio\14-10-2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\opticacuantica\Documents\Mateo Rubio\15-10-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="159">
   <si>
     <t>*** BeamMaster USB Measurement system, Version 1.5.0.3 ***</t>
   </si>
@@ -128,367 +128,379 @@
     <t>0,0</t>
   </si>
   <si>
-    <t>-673,7</t>
-  </si>
-  <si>
-    <t>260,2</t>
-  </si>
-  <si>
-    <t>261,8</t>
+    <t>817,4</t>
+  </si>
+  <si>
+    <t>283,7</t>
+  </si>
+  <si>
+    <t>264,2</t>
+  </si>
+  <si>
+    <t>328,6</t>
+  </si>
+  <si>
+    <t>205,7</t>
+  </si>
+  <si>
+    <t>254,1</t>
+  </si>
+  <si>
+    <t>243,3</t>
+  </si>
+  <si>
+    <t>0,2</t>
+  </si>
+  <si>
+    <t>817,1</t>
+  </si>
+  <si>
+    <t>277,6</t>
+  </si>
+  <si>
+    <t>264,5</t>
+  </si>
+  <si>
+    <t>325,1</t>
+  </si>
+  <si>
+    <t>203,3</t>
+  </si>
+  <si>
+    <t>255,6</t>
+  </si>
+  <si>
+    <t>242,8</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>289,2</t>
+  </si>
+  <si>
+    <t>266,7</t>
   </si>
   <si>
     <t>324,6</t>
   </si>
   <si>
-    <t>175,7</t>
-  </si>
-  <si>
-    <t>251,5</t>
-  </si>
-  <si>
-    <t>246,3</t>
-  </si>
-  <si>
-    <t>0,2</t>
-  </si>
-  <si>
-    <t>-671,6</t>
-  </si>
-  <si>
-    <t>259,0</t>
-  </si>
-  <si>
-    <t>261,5</t>
+    <t>222,3</t>
+  </si>
+  <si>
+    <t>253,9</t>
+  </si>
+  <si>
+    <t>245,0</t>
+  </si>
+  <si>
+    <t>0,6</t>
+  </si>
+  <si>
+    <t>281,5</t>
+  </si>
+  <si>
+    <t>264,8</t>
+  </si>
+  <si>
+    <t>323,1</t>
+  </si>
+  <si>
+    <t>212,1</t>
+  </si>
+  <si>
+    <t>255,0</t>
+  </si>
+  <si>
+    <t>245,3</t>
+  </si>
+  <si>
+    <t>0,8</t>
+  </si>
+  <si>
+    <t>817,9</t>
+  </si>
+  <si>
+    <t>281,2</t>
+  </si>
+  <si>
+    <t>326,1</t>
+  </si>
+  <si>
+    <t>209,4</t>
+  </si>
+  <si>
+    <t>243,1</t>
+  </si>
+  <si>
+    <t>1,0</t>
+  </si>
+  <si>
+    <t>284,9</t>
+  </si>
+  <si>
+    <t>325,3</t>
+  </si>
+  <si>
+    <t>215,6</t>
+  </si>
+  <si>
+    <t>255,7</t>
+  </si>
+  <si>
+    <t>243,4</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>289,9</t>
+  </si>
+  <si>
+    <t>265,3</t>
+  </si>
+  <si>
+    <t>321,4</t>
+  </si>
+  <si>
+    <t>226,1</t>
+  </si>
+  <si>
+    <t>243,5</t>
+  </si>
+  <si>
+    <t>1,4</t>
+  </si>
+  <si>
+    <t>817,7</t>
+  </si>
+  <si>
+    <t>282,3</t>
+  </si>
+  <si>
+    <t>264,4</t>
+  </si>
+  <si>
+    <t>328,1</t>
+  </si>
+  <si>
+    <t>204,9</t>
+  </si>
+  <si>
+    <t>255,5</t>
+  </si>
+  <si>
+    <t>244,1</t>
+  </si>
+  <si>
+    <t>1,6</t>
+  </si>
+  <si>
+    <t>819,0</t>
+  </si>
+  <si>
+    <t>282,4</t>
+  </si>
+  <si>
+    <t>323,9</t>
+  </si>
+  <si>
+    <t>212,6</t>
+  </si>
+  <si>
+    <t>256,0</t>
+  </si>
+  <si>
+    <t>245,9</t>
+  </si>
+  <si>
+    <t>1,8</t>
+  </si>
+  <si>
+    <t>818,7</t>
+  </si>
+  <si>
+    <t>292,6</t>
+  </si>
+  <si>
+    <t>264,9</t>
+  </si>
+  <si>
+    <t>324,3</t>
+  </si>
+  <si>
+    <t>225,0</t>
+  </si>
+  <si>
+    <t>255,3</t>
+  </si>
+  <si>
+    <t>244,8</t>
+  </si>
+  <si>
+    <t>2,0</t>
+  </si>
+  <si>
+    <t>287,7</t>
+  </si>
+  <si>
+    <t>266,4</t>
+  </si>
+  <si>
+    <t>326,3</t>
+  </si>
+  <si>
+    <t>217,4</t>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>819,8</t>
+  </si>
+  <si>
+    <t>279,7</t>
+  </si>
+  <si>
+    <t>265,9</t>
+  </si>
+  <si>
+    <t>323,6</t>
+  </si>
+  <si>
+    <t>210,2</t>
+  </si>
+  <si>
+    <t>254,9</t>
+  </si>
+  <si>
+    <t>245,1</t>
+  </si>
+  <si>
+    <t>2,4</t>
+  </si>
+  <si>
+    <t>289,1</t>
+  </si>
+  <si>
+    <t>265,5</t>
+  </si>
+  <si>
+    <t>324,0</t>
+  </si>
+  <si>
+    <t>221,5</t>
+  </si>
+  <si>
+    <t>255,8</t>
+  </si>
+  <si>
+    <t>245,2</t>
+  </si>
+  <si>
+    <t>2,6</t>
+  </si>
+  <si>
+    <t>818,2</t>
+  </si>
+  <si>
+    <t>289,0</t>
+  </si>
+  <si>
+    <t>262,9</t>
+  </si>
+  <si>
+    <t>324,5</t>
+  </si>
+  <si>
+    <t>217,6</t>
+  </si>
+  <si>
+    <t>2,8</t>
+  </si>
+  <si>
+    <t>287,8</t>
+  </si>
+  <si>
+    <t>323,0</t>
+  </si>
+  <si>
+    <t>221,8</t>
+  </si>
+  <si>
+    <t>3,0</t>
+  </si>
+  <si>
+    <t>283,9</t>
+  </si>
+  <si>
+    <t>267,4</t>
+  </si>
+  <si>
+    <t>217,1</t>
+  </si>
+  <si>
+    <t>3,2</t>
+  </si>
+  <si>
+    <t>818,5</t>
+  </si>
+  <si>
+    <t>281,3</t>
+  </si>
+  <si>
+    <t>266,8</t>
   </si>
   <si>
     <t>325,5</t>
   </si>
   <si>
-    <t>171,7</t>
-  </si>
-  <si>
-    <t>252,2</t>
-  </si>
-  <si>
-    <t>248,1</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>-674,0</t>
-  </si>
-  <si>
-    <t>259,8</t>
-  </si>
-  <si>
-    <t>260,6</t>
-  </si>
-  <si>
-    <t>327,1</t>
-  </si>
-  <si>
-    <t>168,5</t>
-  </si>
-  <si>
-    <t>251,7</t>
-  </si>
-  <si>
-    <t>246,5</t>
-  </si>
-  <si>
-    <t>0,6</t>
-  </si>
-  <si>
-    <t>-672,4</t>
-  </si>
-  <si>
-    <t>261,1</t>
-  </si>
-  <si>
-    <t>260,8</t>
-  </si>
-  <si>
-    <t>312,7</t>
-  </si>
-  <si>
-    <t>196,1</t>
-  </si>
-  <si>
-    <t>252,1</t>
-  </si>
-  <si>
-    <t>246,2</t>
-  </si>
-  <si>
-    <t>0,8</t>
-  </si>
-  <si>
-    <t>-673,5</t>
-  </si>
-  <si>
-    <t>258,8</t>
-  </si>
-  <si>
-    <t>258,9</t>
-  </si>
-  <si>
-    <t>321,9</t>
-  </si>
-  <si>
-    <t>174,3</t>
-  </si>
-  <si>
-    <t>252,9</t>
-  </si>
-  <si>
-    <t>246,4</t>
-  </si>
-  <si>
-    <t>1,0</t>
-  </si>
-  <si>
-    <t>258,6</t>
-  </si>
-  <si>
-    <t>262,3</t>
-  </si>
-  <si>
-    <t>321,8</t>
-  </si>
-  <si>
-    <t>179,1</t>
-  </si>
-  <si>
-    <t>250,6</t>
-  </si>
-  <si>
-    <t>247,2</t>
-  </si>
-  <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>260,0</t>
-  </si>
-  <si>
-    <t>321,4</t>
-  </si>
-  <si>
-    <t>176,9</t>
-  </si>
-  <si>
-    <t>248,2</t>
-  </si>
-  <si>
-    <t>1,4</t>
-  </si>
-  <si>
-    <t>-672,7</t>
-  </si>
-  <si>
-    <t>259,5</t>
-  </si>
-  <si>
-    <t>319,3</t>
-  </si>
-  <si>
-    <t>181,7</t>
-  </si>
-  <si>
-    <t>248,7</t>
-  </si>
-  <si>
-    <t>1,6</t>
-  </si>
-  <si>
-    <t>259,1</t>
-  </si>
-  <si>
-    <t>258,4</t>
-  </si>
-  <si>
-    <t>322,3</t>
-  </si>
-  <si>
-    <t>173,3</t>
-  </si>
-  <si>
-    <t>1,8</t>
-  </si>
-  <si>
-    <t>-673,2</t>
-  </si>
-  <si>
-    <t>257,6</t>
-  </si>
-  <si>
-    <t>261,2</t>
-  </si>
-  <si>
-    <t>320,1</t>
-  </si>
-  <si>
-    <t>179,2</t>
-  </si>
-  <si>
-    <t>247,1</t>
-  </si>
-  <si>
-    <t>2,0</t>
-  </si>
-  <si>
-    <t>-671,9</t>
-  </si>
-  <si>
-    <t>258,1</t>
-  </si>
-  <si>
-    <t>262,4</t>
-  </si>
-  <si>
-    <t>321,6</t>
-  </si>
-  <si>
-    <t>178,9</t>
-  </si>
-  <si>
-    <t>246,1</t>
-  </si>
-  <si>
-    <t>2,2</t>
-  </si>
-  <si>
-    <t>259,2</t>
-  </si>
-  <si>
-    <t>261,6</t>
-  </si>
-  <si>
-    <t>317,5</t>
-  </si>
-  <si>
-    <t>186,5</t>
-  </si>
-  <si>
-    <t>245,9</t>
-  </si>
-  <si>
-    <t>2,4</t>
-  </si>
-  <si>
-    <t>-672,1</t>
-  </si>
-  <si>
-    <t>260,5</t>
-  </si>
-  <si>
-    <t>265,2</t>
-  </si>
-  <si>
-    <t>322,8</t>
-  </si>
-  <si>
-    <t>184,5</t>
-  </si>
-  <si>
-    <t>250,8</t>
-  </si>
-  <si>
-    <t>244,8</t>
-  </si>
-  <si>
-    <t>2,6</t>
-  </si>
-  <si>
-    <t>315,0</t>
-  </si>
-  <si>
-    <t>189,7</t>
-  </si>
-  <si>
-    <t>251,9</t>
-  </si>
-  <si>
-    <t>247,7</t>
-  </si>
-  <si>
-    <t>2,8</t>
-  </si>
-  <si>
-    <t>-674,3</t>
-  </si>
-  <si>
-    <t>260,7</t>
-  </si>
-  <si>
-    <t>319,7</t>
-  </si>
-  <si>
-    <t>182,7</t>
-  </si>
-  <si>
-    <t>3,0</t>
-  </si>
-  <si>
-    <t>262,6</t>
-  </si>
-  <si>
-    <t>318,0</t>
-  </si>
-  <si>
-    <t>186,7</t>
-  </si>
-  <si>
-    <t>3,2</t>
-  </si>
-  <si>
-    <t>261,4</t>
-  </si>
-  <si>
-    <t>317,8</t>
-  </si>
-  <si>
-    <t>189,3</t>
-  </si>
-  <si>
-    <t>250,9</t>
+    <t>210,5</t>
   </si>
   <si>
     <t>3,4</t>
   </si>
   <si>
-    <t>313,7</t>
-  </si>
-  <si>
-    <t>190,9</t>
-  </si>
-  <si>
-    <t>252,6</t>
-  </si>
-  <si>
-    <t>246,0</t>
+    <t>283,8</t>
+  </si>
+  <si>
+    <t>327,3</t>
+  </si>
+  <si>
+    <t>207,9</t>
+  </si>
+  <si>
+    <t>244,9</t>
   </si>
   <si>
     <t>3,6</t>
   </si>
   <si>
-    <t>183,2</t>
+    <t>281,7</t>
+  </si>
+  <si>
+    <t>329,0</t>
+  </si>
+  <si>
+    <t>202,4</t>
+  </si>
+  <si>
+    <t>243,0</t>
   </si>
   <si>
     <t>3,8</t>
   </si>
   <si>
-    <t>262,2</t>
-  </si>
-  <si>
-    <t>320,4</t>
-  </si>
-  <si>
-    <t>185,1</t>
-  </si>
-  <si>
-    <t>250,3</t>
+    <t>282,7</t>
+  </si>
+  <si>
+    <t>328,0</t>
+  </si>
+  <si>
+    <t>206,1</t>
+  </si>
+  <si>
+    <t>254,0</t>
   </si>
 </sst>
 </file>
@@ -829,7 +841,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="1">
-        <v>46309</v>
+        <v>46310</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -837,7 +849,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="2">
-        <v>0.59086805555555555</v>
+        <v>0.76569444444444434</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -978,7 +990,7 @@
         <v>34</v>
       </c>
       <c r="C23">
-        <v>2654</v>
+        <v>1064</v>
       </c>
       <c r="D23" t="s">
         <v>35</v>
@@ -1007,7 +1019,7 @@
         <v>42</v>
       </c>
       <c r="C24">
-        <v>2655</v>
+        <v>1064</v>
       </c>
       <c r="D24" t="s">
         <v>43</v>
@@ -1033,202 +1045,202 @@
         <v>49</v>
       </c>
       <c r="B25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25">
+        <v>1063</v>
+      </c>
+      <c r="D25" t="s">
         <v>50</v>
       </c>
-      <c r="C25">
-        <v>2655</v>
-      </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>51</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>52</v>
       </c>
-      <c r="F25" t="s">
+      <c r="G25" t="s">
         <v>53</v>
       </c>
-      <c r="G25" t="s">
+      <c r="H25" t="s">
         <v>54</v>
       </c>
-      <c r="H25" t="s">
+      <c r="I25" t="s">
         <v>55</v>
-      </c>
-      <c r="I25" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26">
+        <v>1063</v>
+      </c>
+      <c r="D26" t="s">
         <v>57</v>
       </c>
-      <c r="B26" t="s">
+      <c r="E26" t="s">
         <v>58</v>
       </c>
-      <c r="C26">
-        <v>2654</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="F26" t="s">
         <v>59</v>
       </c>
-      <c r="E26" t="s">
+      <c r="G26" t="s">
         <v>60</v>
       </c>
-      <c r="F26" t="s">
+      <c r="H26" t="s">
         <v>61</v>
       </c>
-      <c r="G26" t="s">
+      <c r="I26" t="s">
         <v>62</v>
-      </c>
-      <c r="H26" t="s">
-        <v>63</v>
-      </c>
-      <c r="I26" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27">
+        <v>1064</v>
+      </c>
+      <c r="D27" t="s">
         <v>65</v>
       </c>
-      <c r="B27" t="s">
+      <c r="E27" t="s">
+        <v>51</v>
+      </c>
+      <c r="F27" t="s">
         <v>66</v>
       </c>
-      <c r="C27">
-        <v>2655</v>
-      </c>
-      <c r="D27" t="s">
+      <c r="G27" t="s">
         <v>67</v>
       </c>
-      <c r="E27" t="s">
+      <c r="H27" t="s">
+        <v>47</v>
+      </c>
+      <c r="I27" t="s">
         <v>68</v>
-      </c>
-      <c r="F27" t="s">
-        <v>69</v>
-      </c>
-      <c r="G27" t="s">
-        <v>70</v>
-      </c>
-      <c r="H27" t="s">
-        <v>71</v>
-      </c>
-      <c r="I27" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>69</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28">
+        <v>1065</v>
+      </c>
+      <c r="D28" t="s">
+        <v>70</v>
+      </c>
+      <c r="E28" t="s">
+        <v>51</v>
+      </c>
+      <c r="F28" t="s">
+        <v>71</v>
+      </c>
+      <c r="G28" t="s">
+        <v>72</v>
+      </c>
+      <c r="H28" t="s">
         <v>73</v>
       </c>
-      <c r="B28" t="s">
-        <v>66</v>
-      </c>
-      <c r="C28">
-        <v>2654</v>
-      </c>
-      <c r="D28" t="s">
+      <c r="I28" t="s">
         <v>74</v>
-      </c>
-      <c r="E28" t="s">
-        <v>75</v>
-      </c>
-      <c r="F28" t="s">
-        <v>76</v>
-      </c>
-      <c r="G28" t="s">
-        <v>77</v>
-      </c>
-      <c r="H28" t="s">
-        <v>78</v>
-      </c>
-      <c r="I28" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>75</v>
+      </c>
+      <c r="B29" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29">
+        <v>1064</v>
+      </c>
+      <c r="D29" t="s">
+        <v>76</v>
+      </c>
+      <c r="E29" t="s">
+        <v>77</v>
+      </c>
+      <c r="F29" t="s">
+        <v>78</v>
+      </c>
+      <c r="G29" t="s">
+        <v>79</v>
+      </c>
+      <c r="H29" t="s">
+        <v>39</v>
+      </c>
+      <c r="I29" t="s">
         <v>80</v>
-      </c>
-      <c r="B29" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29">
-        <v>2656</v>
-      </c>
-      <c r="D29" t="s">
-        <v>67</v>
-      </c>
-      <c r="E29" t="s">
-        <v>81</v>
-      </c>
-      <c r="F29" t="s">
-        <v>82</v>
-      </c>
-      <c r="G29" t="s">
-        <v>83</v>
-      </c>
-      <c r="H29" t="s">
-        <v>63</v>
-      </c>
-      <c r="I29" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>81</v>
+      </c>
+      <c r="B30" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30">
+        <v>1063</v>
+      </c>
+      <c r="D30" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" t="s">
+        <v>84</v>
+      </c>
+      <c r="F30" t="s">
         <v>85</v>
       </c>
-      <c r="B30" t="s">
+      <c r="G30" t="s">
         <v>86</v>
       </c>
-      <c r="C30">
-        <v>2656</v>
-      </c>
-      <c r="D30" t="s">
+      <c r="H30" t="s">
         <v>87</v>
       </c>
-      <c r="E30" t="s">
-        <v>81</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="I30" t="s">
         <v>88</v>
-      </c>
-      <c r="G30" t="s">
-        <v>89</v>
-      </c>
-      <c r="H30" t="s">
-        <v>47</v>
-      </c>
-      <c r="I30" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>89</v>
+      </c>
+      <c r="B31" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31">
+        <v>1066</v>
+      </c>
+      <c r="D31" t="s">
         <v>91</v>
       </c>
-      <c r="B31" t="s">
-        <v>86</v>
-      </c>
-      <c r="C31">
-        <v>2655</v>
-      </c>
-      <c r="D31" t="s">
+      <c r="E31" t="s">
+        <v>77</v>
+      </c>
+      <c r="F31" t="s">
         <v>92</v>
       </c>
-      <c r="E31" t="s">
+      <c r="G31" t="s">
         <v>93</v>
       </c>
-      <c r="F31" t="s">
+      <c r="H31" t="s">
         <v>94</v>
       </c>
-      <c r="G31" t="s">
+      <c r="I31" t="s">
         <v>95</v>
-      </c>
-      <c r="H31" t="s">
-        <v>47</v>
-      </c>
-      <c r="I31" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
@@ -1239,7 +1251,7 @@
         <v>97</v>
       </c>
       <c r="C32">
-        <v>2654</v>
+        <v>1065</v>
       </c>
       <c r="D32" t="s">
         <v>98</v>
@@ -1254,21 +1266,21 @@
         <v>101</v>
       </c>
       <c r="H32" t="s">
-        <v>63</v>
+        <v>102</v>
       </c>
       <c r="I32" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B33" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="C33">
-        <v>2656</v>
+        <v>1064</v>
       </c>
       <c r="D33" t="s">
         <v>105</v>
@@ -1283,21 +1295,21 @@
         <v>108</v>
       </c>
       <c r="H33" t="s">
-        <v>39</v>
+        <v>87</v>
       </c>
       <c r="I33" t="s">
-        <v>109</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>109</v>
+      </c>
+      <c r="B34" t="s">
         <v>110</v>
       </c>
-      <c r="B34" t="s">
-        <v>58</v>
-      </c>
       <c r="C34">
-        <v>2654</v>
+        <v>1065</v>
       </c>
       <c r="D34" t="s">
         <v>111</v>
@@ -1312,21 +1324,21 @@
         <v>114</v>
       </c>
       <c r="H34" t="s">
-        <v>63</v>
+        <v>115</v>
       </c>
       <c r="I34" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B35" t="s">
-        <v>117</v>
+        <v>64</v>
       </c>
       <c r="C35">
-        <v>2655</v>
+        <v>1062</v>
       </c>
       <c r="D35" t="s">
         <v>118</v>
@@ -1352,45 +1364,45 @@
         <v>124</v>
       </c>
       <c r="B36" t="s">
-        <v>66</v>
+        <v>125</v>
       </c>
       <c r="C36">
-        <v>2652</v>
+        <v>1065</v>
       </c>
       <c r="D36" t="s">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="E36" t="s">
-        <v>59</v>
+        <v>127</v>
       </c>
       <c r="F36" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G36" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H36" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="I36" t="s">
-        <v>128</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B37" t="s">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="C37">
-        <v>2654</v>
+        <v>1064</v>
       </c>
       <c r="D37" t="s">
         <v>131</v>
       </c>
       <c r="E37" t="s">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="F37" t="s">
         <v>132</v>
@@ -1399,10 +1411,10 @@
         <v>133</v>
       </c>
       <c r="H37" t="s">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="I37" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
@@ -1410,28 +1422,28 @@
         <v>134</v>
       </c>
       <c r="B38" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="C38">
-        <v>2652</v>
+        <v>1065</v>
       </c>
       <c r="D38" t="s">
-        <v>43</v>
+        <v>135</v>
       </c>
       <c r="E38" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F38" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="G38" t="s">
         <v>137</v>
       </c>
       <c r="H38" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="I38" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
@@ -1439,115 +1451,115 @@
         <v>138</v>
       </c>
       <c r="B39" t="s">
-        <v>86</v>
+        <v>139</v>
       </c>
       <c r="C39">
-        <v>2654</v>
+        <v>1064</v>
       </c>
       <c r="D39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E39" t="s">
-        <v>36</v>
+        <v>141</v>
       </c>
       <c r="F39" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G39" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H39" t="s">
-        <v>142</v>
+        <v>102</v>
       </c>
       <c r="I39" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B40" t="s">
-        <v>117</v>
+        <v>139</v>
       </c>
       <c r="C40">
-        <v>2654</v>
+        <v>1065</v>
       </c>
       <c r="D40" t="s">
-        <v>92</v>
+        <v>145</v>
       </c>
       <c r="E40" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F40" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G40" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="H40" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="I40" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B41" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C41">
-        <v>2654</v>
+        <v>1064</v>
       </c>
       <c r="D41" t="s">
-        <v>98</v>
+        <v>150</v>
       </c>
       <c r="E41" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="F41" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="G41" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H41" t="s">
-        <v>122</v>
+        <v>73</v>
       </c>
       <c r="I41" t="s">
-        <v>109</v>
+        <v>153</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B42" t="s">
-        <v>86</v>
+        <v>34</v>
       </c>
       <c r="C42">
-        <v>2654</v>
+        <v>1065</v>
       </c>
       <c r="D42" t="s">
-        <v>59</v>
+        <v>155</v>
       </c>
       <c r="E42" t="s">
-        <v>151</v>
+        <v>99</v>
       </c>
       <c r="F42" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G42" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H42" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="I42" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
